--- a/input/Data_Historical.xlsx
+++ b/input/Data_Historical.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\epish\PycharmProjects\endemo_git\pythonProject\draft_endemo\input\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\epish\PycharmProjects\endemo_git\pythonProject\endemo\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7999AFF2-EB8F-473D-B1CF-BE1531875897}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{163ED172-8FB7-4E80-8BA8-D91EB807C75A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="2" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="64">
   <si>
     <t>Region</t>
   </si>
@@ -97,9 +97,6 @@
   </si>
   <si>
     <t>HEAT</t>
-  </si>
-  <si>
-    <t>TOTAL</t>
   </si>
   <si>
     <t>Q1</t>
@@ -355,18 +352,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="3">
@@ -441,7 +432,7 @@
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="11" fillId="0" borderId="0" xfId="12" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="13">
     <cellStyle name="Comma 2" xfId="4" xr:uid="{A70710B6-1D5C-4F83-BE45-02569B1302DC}"/>
@@ -758,12 +749,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1481D4CD-D5CE-4563-99FF-4E41155141F5}">
-  <dimension ref="A1:CB23"/>
+  <dimension ref="A1:CB25"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:80" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>0</v>
@@ -781,16 +772,16 @@
         <v>4</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H1" s="2" t="s">
         <v>5</v>
       </c>
       <c r="I1" t="s">
+        <v>29</v>
+      </c>
+      <c r="J1" t="s">
         <v>30</v>
-      </c>
-      <c r="J1" t="s">
-        <v>31</v>
       </c>
       <c r="K1" s="2" t="s">
         <v>6</v>
@@ -1000,12 +991,12 @@
         <v>7</v>
       </c>
       <c r="CB1" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:80" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B2" t="s">
         <v>9</v>
@@ -1020,7 +1011,7 @@
         <v>13</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BO2">
         <v>42645</v>
@@ -1053,12 +1044,12 @@
         <v>37234</v>
       </c>
       <c r="BY2" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3" spans="1:80" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B3" t="s">
         <v>10</v>
@@ -1073,13 +1064,13 @@
         <v>13</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BR3">
         <v>0</v>
       </c>
       <c r="BY3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="4" spans="1:80" x14ac:dyDescent="0.3">
@@ -1102,13 +1093,13 @@
         <v>18</v>
       </c>
       <c r="K4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BR4">
         <v>2</v>
       </c>
       <c r="BY4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="5" spans="1:80" x14ac:dyDescent="0.3">
@@ -1131,13 +1122,13 @@
         <v>19</v>
       </c>
       <c r="K5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BR5">
         <v>0</v>
       </c>
       <c r="BY5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="6" spans="1:80" x14ac:dyDescent="0.3">
@@ -1160,16 +1151,16 @@
         <v>20</v>
       </c>
       <c r="H6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BR6">
         <v>4</v>
       </c>
       <c r="BY6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="7" spans="1:80" x14ac:dyDescent="0.3">
@@ -1192,16 +1183,16 @@
         <v>20</v>
       </c>
       <c r="H7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BR7">
         <v>2</v>
       </c>
       <c r="BY7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="8" spans="1:80" x14ac:dyDescent="0.3">
@@ -1224,16 +1215,16 @@
         <v>20</v>
       </c>
       <c r="H8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BR8">
         <v>17</v>
       </c>
       <c r="BY8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="9" spans="1:80" x14ac:dyDescent="0.3">
@@ -1256,16 +1247,16 @@
         <v>20</v>
       </c>
       <c r="H9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BR9">
         <v>75</v>
       </c>
       <c r="BY9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="10" spans="1:80" x14ac:dyDescent="0.3">
@@ -1288,16 +1279,16 @@
         <v>20</v>
       </c>
       <c r="H10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BR10">
         <v>0</v>
       </c>
       <c r="BY10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="11" spans="1:80" x14ac:dyDescent="0.3">
@@ -1323,13 +1314,13 @@
       <c r="I11" s="13"/>
       <c r="J11" s="13"/>
       <c r="K11" s="13" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BR11">
         <v>19</v>
       </c>
       <c r="BY11" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="12" spans="1:80" x14ac:dyDescent="0.3">
@@ -1346,22 +1337,19 @@
         <v>14</v>
       </c>
       <c r="F12" t="s">
-        <v>16</v>
-      </c>
-      <c r="G12" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="H12" s="13"/>
-      <c r="I12" s="13"/>
-      <c r="J12" s="13"/>
-      <c r="K12" s="13" t="s">
-        <v>27</v>
+        <v>17</v>
+      </c>
+      <c r="G12" t="s">
+        <v>18</v>
+      </c>
+      <c r="K12" t="s">
+        <v>26</v>
       </c>
       <c r="BR12">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="BY12" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="13" spans="1:80" x14ac:dyDescent="0.3">
@@ -1381,16 +1369,16 @@
         <v>17</v>
       </c>
       <c r="G13" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K13" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BR13">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="BY13" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="14" spans="1:80" x14ac:dyDescent="0.3">
@@ -1410,16 +1398,19 @@
         <v>17</v>
       </c>
       <c r="G14" t="s">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="H14" t="s">
+        <v>21</v>
       </c>
       <c r="K14" t="s">
         <v>27</v>
       </c>
       <c r="BR14">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="BY14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="15" spans="1:80" x14ac:dyDescent="0.3">
@@ -1445,13 +1436,13 @@
         <v>22</v>
       </c>
       <c r="K15" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BR15">
         <v>3</v>
       </c>
       <c r="BY15" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="16" spans="1:80" x14ac:dyDescent="0.3">
@@ -1470,20 +1461,24 @@
       <c r="F16" t="s">
         <v>17</v>
       </c>
-      <c r="G16" t="s">
+      <c r="G16" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="H16" t="s">
+      <c r="H16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="K16" t="s">
-        <v>28</v>
-      </c>
+      <c r="I16" s="13"/>
+      <c r="J16" s="13"/>
+      <c r="K16" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="L16" s="13"/>
+      <c r="M16" s="13"/>
       <c r="BR16">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="BY16" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="17" spans="2:77" x14ac:dyDescent="0.3">
@@ -1502,20 +1497,24 @@
       <c r="F17" t="s">
         <v>17</v>
       </c>
-      <c r="G17" t="s">
+      <c r="G17" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="H17" t="s">
+      <c r="H17" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="K17" t="s">
-        <v>28</v>
-      </c>
+      <c r="I17" s="13"/>
+      <c r="J17" s="13"/>
+      <c r="K17" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="L17" s="13"/>
+      <c r="M17" s="13"/>
       <c r="BR17">
-        <v>19</v>
+        <v>75</v>
       </c>
       <c r="BY17" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="18" spans="2:77" x14ac:dyDescent="0.3">
@@ -1534,20 +1533,24 @@
       <c r="F18" t="s">
         <v>17</v>
       </c>
-      <c r="G18" t="s">
+      <c r="G18" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="H18" t="s">
+      <c r="H18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="K18" t="s">
-        <v>28</v>
-      </c>
+      <c r="I18" s="13"/>
+      <c r="J18" s="13"/>
+      <c r="K18" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="L18" s="13"/>
+      <c r="M18" s="13"/>
       <c r="BR18">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="BY18" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
     </row>
     <row r="19" spans="2:77" x14ac:dyDescent="0.3">
@@ -1566,20 +1569,22 @@
       <c r="F19" t="s">
         <v>17</v>
       </c>
-      <c r="G19" t="s">
+      <c r="G19" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="H19" t="s">
+      <c r="H19" s="13"/>
+      <c r="I19" s="13"/>
+      <c r="J19" s="13"/>
+      <c r="K19" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="K19" t="s">
-        <v>28</v>
-      </c>
+      <c r="L19" s="13"/>
+      <c r="M19" s="13"/>
       <c r="BR19">
         <v>0</v>
       </c>
       <c r="BY19" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
     </row>
     <row r="20" spans="2:77" x14ac:dyDescent="0.3">
@@ -1593,25 +1598,25 @@
         <v>12</v>
       </c>
       <c r="E20" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F20" t="s">
-        <v>17</v>
-      </c>
-      <c r="G20" s="13" t="s">
-        <v>20</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="G20" s="13"/>
       <c r="H20" s="13"/>
       <c r="I20" s="13"/>
       <c r="J20" s="13"/>
       <c r="K20" s="13" t="s">
         <v>27</v>
       </c>
+      <c r="L20" s="13"/>
+      <c r="M20" s="13"/>
       <c r="BR20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="BY20" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
     </row>
     <row r="21" spans="2:77" x14ac:dyDescent="0.3">
@@ -1625,78 +1630,62 @@
         <v>12</v>
       </c>
       <c r="E21" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F21" t="s">
         <v>17</v>
       </c>
-      <c r="G21" s="13" t="s">
-        <v>21</v>
-      </c>
+      <c r="G21" s="13"/>
       <c r="H21" s="13"/>
       <c r="I21" s="13"/>
       <c r="J21" s="13"/>
       <c r="K21" s="13" t="s">
         <v>27</v>
       </c>
+      <c r="L21" s="13"/>
+      <c r="M21" s="13"/>
       <c r="BR21">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="BY21" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
     </row>
     <row r="22" spans="2:77" x14ac:dyDescent="0.3">
-      <c r="B22" t="s">
-        <v>10</v>
-      </c>
-      <c r="C22" t="s">
-        <v>11</v>
-      </c>
-      <c r="D22" t="s">
-        <v>12</v>
-      </c>
-      <c r="E22" t="s">
-        <v>15</v>
-      </c>
-      <c r="F22" t="s">
-        <v>16</v>
-      </c>
-      <c r="K22" t="s">
-        <v>28</v>
-      </c>
-      <c r="BR22">
-        <v>100</v>
-      </c>
-      <c r="BY22" t="s">
-        <v>48</v>
-      </c>
+      <c r="G22" s="13"/>
+      <c r="H22" s="13"/>
+      <c r="I22" s="13"/>
+      <c r="J22" s="13"/>
+      <c r="K22" s="13"/>
+      <c r="L22" s="13"/>
+      <c r="M22" s="13"/>
     </row>
     <row r="23" spans="2:77" x14ac:dyDescent="0.3">
-      <c r="B23" t="s">
-        <v>10</v>
-      </c>
-      <c r="C23" t="s">
-        <v>11</v>
-      </c>
-      <c r="D23" t="s">
-        <v>12</v>
-      </c>
-      <c r="E23" t="s">
-        <v>15</v>
-      </c>
-      <c r="F23" t="s">
-        <v>17</v>
-      </c>
-      <c r="K23" t="s">
-        <v>28</v>
-      </c>
-      <c r="BR23">
-        <v>0</v>
-      </c>
-      <c r="BY23" t="s">
-        <v>48</v>
-      </c>
+      <c r="G23" s="13"/>
+      <c r="H23" s="13"/>
+      <c r="I23" s="13"/>
+      <c r="J23" s="13"/>
+      <c r="K23" s="13"/>
+      <c r="L23" s="13"/>
+      <c r="M23" s="13"/>
+    </row>
+    <row r="24" spans="2:77" x14ac:dyDescent="0.3">
+      <c r="G24" s="13"/>
+      <c r="H24" s="13"/>
+      <c r="I24" s="13"/>
+      <c r="J24" s="13"/>
+      <c r="K24" s="13"/>
+      <c r="L24" s="13"/>
+      <c r="M24" s="13"/>
+    </row>
+    <row r="25" spans="2:77" x14ac:dyDescent="0.3">
+      <c r="G25" s="13"/>
+      <c r="H25" s="13"/>
+      <c r="I25" s="13"/>
+      <c r="J25" s="13"/>
+      <c r="K25" s="13"/>
+      <c r="L25" s="13"/>
+      <c r="M25" s="13"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1714,89 +1703,89 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D4" t="s">
         <v>39</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>40</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>41</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>42</v>
       </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
         <v>43</v>
       </c>
-      <c r="H4" t="s">
+      <c r="I4" t="s">
         <v>44</v>
       </c>
-      <c r="I4" t="s">
+      <c r="J4" s="5" t="s">
         <v>45</v>
-      </c>
-      <c r="J4" s="5" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D5" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="E5" t="s">
         <v>49</v>
-      </c>
-      <c r="E5" t="s">
-        <v>50</v>
       </c>
       <c r="F5" s="9"/>
       <c r="G5" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="H5" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="H5" s="5" t="s">
-        <v>52</v>
-      </c>
       <c r="I5" s="6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B6" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="C6" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="E6" t="s">
         <v>57</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" s="6" t="s">
         <v>58</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>59</v>
       </c>
       <c r="I6" s="6"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B7" t="s">
+        <v>59</v>
+      </c>
+      <c r="C7" t="s">
         <v>60</v>
-      </c>
-      <c r="C7" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
@@ -1804,13 +1793,13 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
+        <v>61</v>
+      </c>
+      <c r="B9" t="s">
         <v>62</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" s="5" t="s">
         <v>63</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
